--- a/terminology/CodeSystem-dlp-lecivepripravky.xlsx
+++ b/terminology/CodeSystem-dlp-lecivepripravky.xlsx
@@ -29,13 +29,13 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>urn:ietf:rfc:3986#URI#?ngen-9?</t>
+    <t>urn:ietf:rfc:3986#Uniform Resource Identifier (URI)#?ngen-9?</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -47,7 +47,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Codesystem of DLP Lecive pripravky</t>
+    <t>DLP Lecive pripravky</t>
   </si>
   <si>
     <t>Status</t>
@@ -89,7 +89,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codesystem of DLP Lecive pripravky. Identification medication.</t>
+    <t>DLP Lecive pripravky - Czech national registry of the pharmaceutical products.</t>
   </si>
   <si>
     <t>Purpose</t>
